--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488277_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488277_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4352</v>
+        <v>1.8361</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3118</v>
+        <v>3.4419</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8766</v>
+        <v>-1.6058</v>
       </c>
       <c r="G2" t="n">
         <v>0.2852</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9267</v>
+        <v>0.3277</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6477</v>
+        <v>0.7779</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.721</v>
+        <v>-0.4502</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6296</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2782</v>
+        <v>0.8973</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1778</v>
+        <v>1.7883</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1004</v>
+        <v>-0.8909</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4558</v>
+        <v>-0.7662</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3428</v>
+        <v>0.2275</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.7985</v>
+        <v>-0.9937</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6382</v>
+        <v>1.0288</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9318</v>
+        <v>0.8629</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.57</v>
+        <v>0.1659</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8175</v>
+        <v>-1.795</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.589</v>
+        <v>-0.6354</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2285</v>
+        <v>-1.1596</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9646</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6781</v>
+        <v>0.7371</v>
       </c>
       <c r="T4" t="n">
-        <v>2.41</v>
+        <v>0.7595</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.732</v>
+        <v>-0.0224</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9442</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7449</v>
+        <v>0.6126</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3232</v>
+        <v>-0.633</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5783</v>
+        <v>1.2457</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2882</v>
+        <v>-1.644</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9893999999999999</v>
+        <v>1.7415</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2776</v>
+        <v>-3.3854</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9564</v>
+        <v>0.3795</v>
       </c>
       <c r="K5" t="n">
-        <v>1.915</v>
+        <v>2.9282</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0415</v>
+        <v>-2.5486</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2447</v>
+        <v>-2.0235</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9255</v>
+        <v>-1.1867</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3191</v>
+        <v>-0.8368</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>3.5205</v>
       </c>
       <c r="S5" t="n">
-        <v>2.644</v>
+        <v>0.2748</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5171</v>
+        <v>0.2114</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1269</v>
+        <v>0.0634</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3155</v>
+        <v>0.3142</v>
       </c>
       <c r="W5" t="n">
         <v>0.6289</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3133</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1314</v>
+        <v>0.1343</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2439</v>
+        <v>-0.1385</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1125</v>
+        <v>0.2728</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7662</v>
+        <v>-2.4558</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2275</v>
+        <v>1.3428</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9937</v>
+        <v>-3.7985</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0288</v>
+        <v>-0.6382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8629</v>
+        <v>1.9318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1659</v>
+        <v>-2.57</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.795</v>
+        <v>-1.8175</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6354</v>
+        <v>-0.589</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1596</v>
+        <v>-1.2285</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>2.9646</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0288</v>
+        <v>0.5341</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2151</v>
+        <v>1.0937</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.244</v>
+        <v>-0.5596</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9442</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4535</v>
+        <v>-0.0864</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7741</v>
+        <v>-0.3823</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3206</v>
+        <v>0.296</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5253</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1134</v>
+        <v>0.2537</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1641</v>
+        <v>0.2276</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0507</v>
+        <v>0.0261</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.899</v>
+        <v>-0.6864</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9723</v>
+        <v>0.6059</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0733</v>
+        <v>-1.2923</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.644</v>
+        <v>-1.2882</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7415</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.3854</v>
+        <v>-2.2776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3795</v>
+        <v>1.9564</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9282</v>
+        <v>1.915</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.5486</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0235</v>
+        <v>-3.2447</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1867</v>
+        <v>-0.9255</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8368</v>
+        <v>-2.3191</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6676</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5205</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2368</v>
+        <v>1.2128</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1279</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.109</v>
+        <v>0.4128</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3142</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
         <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3147</v>
+        <v>-0.3133</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6623</v>
+        <v>-1.392</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7694</v>
+        <v>-0.6715</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8929</v>
+        <v>-0.7206</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8977</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3089</v>
+        <v>0.5792</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3246</v>
+        <v>0.4225</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0157</v>
+        <v>0.1567</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5487</v>
+        <v>-3.5088</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.469</v>
+        <v>-1.109</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0797</v>
+        <v>-2.3998</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6078</v>
@@ -1234,13 +1234,13 @@
         <v>3.891</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0413</v>
+        <v>1.0813</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7213000000000001</v>
+        <v>1.0813</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3201</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3147</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9484</v>
+        <v>-3.752</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1345</v>
+        <v>-2.0366</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8139</v>
+        <v>-1.7154</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4605</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2291</v>
+        <v>-0.0326</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0102</v>
+        <v>0.0883</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2622</v>
+        <v>-4.4186</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7543</v>
+        <v>-4.8615</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4921</v>
+        <v>0.4429</v>
       </c>
       <c r="G12" t="n">
         <v>-3.336</v>
@@ -1390,13 +1390,13 @@
         <v>3.3352</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2416</v>
+        <v>-0.3979</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1279</v>
+        <v>-0.235</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1137</v>
+        <v>-0.1629</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3141</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.5961</v>
+        <v>-8.775599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2286</v>
+        <v>-2.408000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.367500000000001</v>
+        <v>-6.3674</v>
       </c>
       <c r="G13" t="n">
         <v>-16.108</v>
@@ -1453,13 +1453,13 @@
         <v>-20.3246</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.616299999999999</v>
+        <v>-7.6163</v>
       </c>
       <c r="O13" t="n">
         <v>-12.7083</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7057</v>
+        <v>3.705699999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.6758</v>
@@ -1468,13 +1468,13 @@
         <v>20.3816</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7493</v>
+        <v>4.5702</v>
       </c>
       <c r="T13" t="n">
-        <v>4.197000000000001</v>
+        <v>5.0179</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4478999999999999</v>
+        <v>-0.4478</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9434</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.4491</v>
+        <v>11.212</v>
       </c>
       <c r="E14" t="n">
-        <v>9.994</v>
+        <v>9.700200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4551</v>
+        <v>1.5118</v>
       </c>
       <c r="G14" t="n">
         <v>8.93</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1485</v>
+        <v>-0.0886</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5609</v>
+        <v>0.2671</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4124</v>
+        <v>-0.3557</v>
       </c>
       <c r="V14" t="n">
         <v>1.2589</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2819</v>
+        <v>2.6893</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4134</v>
+        <v>1.0424</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8685</v>
+        <v>1.6469</v>
       </c>
       <c r="G15" t="n">
         <v>1.242</v>
@@ -1624,13 +1624,13 @@
         <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9663</v>
+        <v>0.3737</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9424</v>
+        <v>0.5714</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0238</v>
+        <v>-0.1977</v>
       </c>
       <c r="V15" t="n">
         <v>1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3222</v>
+        <v>2.0581</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1757</v>
+        <v>0.314</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4979</v>
+        <v>1.7441</v>
       </c>
       <c r="G16" t="n">
         <v>1.4528</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8717</v>
+        <v>-0.1359</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4501</v>
+        <v>0.0395</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4216</v>
+        <v>-0.1754</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7995</v>
+        <v>1.5921</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6174</v>
+        <v>2.107</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8179</v>
+        <v>-0.515</v>
       </c>
       <c r="G17" t="n">
         <v>0.8895999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6285</v>
+        <v>-0.836</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.909</v>
+        <v>-0.4194</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7195</v>
+        <v>-0.4166</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3144</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1492</v>
+        <v>0.3291</v>
       </c>
       <c r="E19" t="n">
         <v>-0.1033</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2526</v>
+        <v>0.4324</v>
       </c>
       <c r="G19" t="n">
         <v>0.2681</v>
@@ -1936,13 +1936,13 @@
         <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1189</v>
+        <v>0.0609</v>
       </c>
       <c r="T19" t="n">
         <v>0.1604</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2793</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5617</v>
+        <v>-0.5313</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0536</v>
+        <v>0.2402</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5081</v>
+        <v>-0.7715</v>
       </c>
       <c r="G20" t="n">
         <v>0.9613</v>
@@ -2014,13 +2014,13 @@
         <v>2.0382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0694</v>
+        <v>0.0998</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2027</v>
+        <v>0.4965</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1333</v>
+        <v>-0.3967</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5188</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6541</v>
+        <v>-0.6558</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5988</v>
+        <v>-2.305</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9446</v>
+        <v>1.6492</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8295</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5091</v>
+        <v>-0.5108</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8754</v>
+        <v>-0.5816</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3663</v>
+        <v>0.0709</v>
       </c>
       <c r="V21" t="n">
         <v>0.3139</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9428</v>
+        <v>-0.8935</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7623</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1805</v>
+        <v>-0.1312</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4759</v>
@@ -2170,13 +2170,13 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1525</v>
+        <v>-0.1032</v>
       </c>
       <c r="T22" t="n">
         <v>0.0759</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2283</v>
+        <v>-0.1791</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3405</v>
+        <v>-1.0376</v>
       </c>
       <c r="E23" t="n">
         <v>1.0439</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3844</v>
+        <v>-2.0814</v>
       </c>
       <c r="G23" t="n">
         <v>3.5087</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1821</v>
+        <v>-0.8792</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1131</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.069</v>
+        <v>-0.766</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2583</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4898</v>
+        <v>-2.219</v>
       </c>
       <c r="E24" t="n">
         <v>-4.017</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5272</v>
+        <v>1.798</v>
       </c>
       <c r="G24" t="n">
         <v>1.1678</v>
@@ -2326,13 +2326,13 @@
         <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3017</v>
+        <v>-1.0309</v>
       </c>
       <c r="T24" t="n">
         <v>-0.092</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2097</v>
+        <v>-0.9389</v>
       </c>
       <c r="V24" t="n">
         <v>2.8321</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0388</v>
+        <v>-2.9163</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6125</v>
+        <v>-1.5146</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4263</v>
+        <v>-1.4017</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6291</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1689</v>
+        <v>-0.0463</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3144</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.596299999999998</v>
+        <v>10.2492</v>
       </c>
       <c r="E26" t="n">
-        <v>6.367599999999999</v>
+        <v>6.367600000000004</v>
       </c>
       <c r="F26" t="n">
-        <v>3.228699999999999</v>
+        <v>3.881600000000001</v>
       </c>
       <c r="G26" t="n">
         <v>16.1079</v>
@@ -2482,13 +2482,13 @@
         <v>16.676</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.7492</v>
+        <v>-3.0965</v>
       </c>
       <c r="T26" t="n">
-        <v>0.448</v>
+        <v>0.4479000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.1972</v>
+        <v>-3.5442</v>
       </c>
       <c r="V26" t="n">
         <v>0.9434999999999996</v>
